--- a/erp-server/erp-server-file/src/main/resources/excel/oms/kolPartnerInfoExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/kolPartnerInfoExport.xlsx
@@ -1,34 +1,50 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>工作表</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>3</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="3" baseType="lpstr">
+      <vt:lpstr>Sheet1</vt:lpstr>
+      <vt:lpstr>Sheet2</vt:lpstr>
+      <vt:lpstr>Sheet3</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <cp:lastModifiedBy>H、</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2006-09-16T00:00:00Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2025-12-03T03:14:48Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="ICV">
+    <vt:lpwstr>7F7DFA33A32D4A58938CE18BC6603B26_12</vt:lpwstr>
+  </property>
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="KSOProductBuildVer">
+    <vt:lpwstr>2052-12.1.0.24034</vt:lpwstr>
+  </property>
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="4" name="CalculationRule">
+    <vt:i4>0</vt:i4>
+  </property>
+</Properties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>达人编码</t>
@@ -76,7 +92,7 @@
     <t>账号名称</t>
   </si>
   <si>
-    <t>粉丝数量</t>
+    <t>粉丝数量(K)</t>
   </si>
   <si>
     <t>主页连接</t>
@@ -153,7 +169,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
@@ -825,7 +841,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1109,7 +1125,36 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T2"/>
@@ -1260,7 +1305,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
@@ -1271,7 +1316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
